--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.141.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.141.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -875,7 +875,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.141.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.141.xlsx
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,9 +431,9 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="41" customWidth="1" min="14" max="14"/>
-    <col width="40" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.141.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.141.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0141.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0141.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -605,16 +605,20 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L2: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN :: the ä¸€</t>
+          <t>L2: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 :: the 一</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L13: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN :: which was â‚¬</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]134</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]134</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L31: isolated marker/symbol line :: 134</t>
@@ -622,7 +626,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L108: isolated marker/symbol line :: 3</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]134</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -645,7 +649,7 @@
       </c>
       <c r="V2" s="1" t="inlineStr">
         <is>
-          <t>L14: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | abbreviation/spacing may be garbled :: â€”your orator and the said C.D.en-</t>
+          <t>L14: abbreviation/spacing may be garbled :: —your orator and the said C.D.en-</t>
         </is>
       </c>
       <c r="W2" s="1" t="inlineStr"/>
@@ -665,7 +669,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>97</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -680,12 +684,12 @@
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L14: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | abbreviation/spacing may be garbled :: â€”your orator and the said C.D.en-</t>
+          <t>L88: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 :: 一, co-</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L114: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: â€” ---------years, (or for an indefinite time) ; that the</t>
+          <t>L13: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: which was €</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -695,7 +699,11 @@
           <t>L32: isolated marker/symbol line :: u</t>
         </is>
       </c>
-      <c r="O3" s="1" t="inlineStr"/>
+      <c r="O3" s="1" t="inlineStr">
+        <is>
+          <t>L108: isolated marker/symbol line :: 3</t>
+        </is>
+      </c>
       <c r="P3" s="1" t="inlineStr"/>
       <c r="Q3" s="1" t="inlineStr">
         <is>
@@ -703,7 +711,11 @@
         </is>
       </c>
       <c r="R3" s="1" t="inlineStr"/>
-      <c r="S3" s="1" t="inlineStr"/>
+      <c r="S3" s="1" t="inlineStr">
+        <is>
+          <t>L121: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • If either party fills a representative character, say that the said</t>
+        </is>
+      </c>
       <c r="T3" s="1" t="inlineStr"/>
       <c r="U3" s="1" t="inlineStr"/>
       <c r="V3" s="1" t="inlineStr"/>
@@ -733,14 +745,10 @@
       <c r="G4" s="1" t="inlineStr"/>
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>L43: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” part of, the</t>
-        </is>
-      </c>
+      <c r="J4" s="1" t="inlineStr"/>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L121: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ If either party fills a representative character, say that the said</t>
+          <t>L121: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • If either party fills a representative character, say that the said</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -774,12 +782,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -788,16 +796,8 @@
       <c r="G5" s="1" t="inlineStr"/>
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
-      <c r="J5" s="1" t="inlineStr">
-        <is>
-          <t>L55: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: (Pray subpenaÃ¦na).</t>
-        </is>
-      </c>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>L127: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: , and the said â€”â€”</t>
-        </is>
-      </c>
+      <c r="J5" s="1" t="inlineStr"/>
+      <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
@@ -843,16 +843,8 @@
       <c r="G6" s="1" t="inlineStr"/>
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr"/>
-      <c r="J6" s="1" t="inlineStr">
-        <is>
-          <t>L88: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN :: ä¸€, co-</t>
-        </is>
-      </c>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>L129: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”is his executor, or administrator, or heir-at-law.</t>
-        </is>
-      </c>
+      <c r="J6" s="1" t="inlineStr"/>
+      <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr"/>
@@ -894,11 +886,7 @@
       <c r="G7" s="1" t="inlineStr"/>
       <c r="H7" s="1" t="inlineStr"/>
       <c r="I7" s="1" t="inlineStr"/>
-      <c r="J7" s="1" t="inlineStr">
-        <is>
-          <t>L98: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” without any difficulty (here state the facts</t>
-        </is>
-      </c>
+      <c r="J7" s="1" t="inlineStr"/>
       <c r="K7" s="1" t="inlineStr"/>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
@@ -950,7 +938,7 @@
       <c r="P8" s="1" t="inlineStr"/>
       <c r="Q8" s="1" t="inlineStr">
         <is>
-          <t>L114: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: â€” ---------years, (or for an indefinite time) ; that the</t>
+          <t>L114: punctuation artifact: double/multiple hyphen :: — ---------years, (or for an indefinite time) ; that the</t>
         </is>
       </c>
       <c r="R8" s="1" t="inlineStr"/>
@@ -1013,12 +1001,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1057,7 +1045,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1096,7 +1084,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1174,7 +1162,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
